--- a/data/nzd0116/nzd0116.xlsx
+++ b/data/nzd0116/nzd0116.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E255"/>
+  <dimension ref="A1:E256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5785,6 +5785,27 @@
         <v>304.02</v>
       </c>
       <c r="E255" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-22 22:05:56+00:00</t>
+        </is>
+      </c>
+      <c r="B256" t="n">
+        <v>350.14</v>
+      </c>
+      <c r="C256" t="n">
+        <v>305.43</v>
+      </c>
+      <c r="D256" t="n">
+        <v>304.49</v>
+      </c>
+      <c r="E256" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -5801,7 +5822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B285"/>
+  <dimension ref="A1:B286"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8654,6 +8675,16 @@
       </c>
       <c r="B285" t="n">
         <v>0.45</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2025-11-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B286" t="n">
+        <v>0.67</v>
       </c>
     </row>
   </sheetData>
@@ -8822,28 +8853,28 @@
         <v>0.0281</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1118112072816214</v>
+        <v>0.1034354006600475</v>
       </c>
       <c r="J2" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K2" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L2" t="n">
-        <v>0.006246674845305278</v>
+        <v>0.005371512187296479</v>
       </c>
       <c r="M2" t="n">
-        <v>8.419564122087893</v>
+        <v>8.42270791959545</v>
       </c>
       <c r="N2" t="n">
-        <v>107.6240107540642</v>
+        <v>107.6642973277303</v>
       </c>
       <c r="O2" t="n">
-        <v>10.37419928255016</v>
+        <v>10.37614077235512</v>
       </c>
       <c r="P2" t="n">
-        <v>358.141100140371</v>
+        <v>358.2281237293733</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -8900,28 +8931,28 @@
         <v>0.0663</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3692948949784011</v>
+        <v>0.3536849567698716</v>
       </c>
       <c r="J3" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K3" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05835336189665263</v>
+        <v>0.05351843832680192</v>
       </c>
       <c r="M3" t="n">
-        <v>8.935262063111468</v>
+        <v>8.968555776738308</v>
       </c>
       <c r="N3" t="n">
-        <v>119.0906021300504</v>
+        <v>120.229456053133</v>
       </c>
       <c r="O3" t="n">
-        <v>10.9128640663233</v>
+        <v>10.96491933637147</v>
       </c>
       <c r="P3" t="n">
-        <v>316.1440412491974</v>
+        <v>316.3062265655955</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -8978,28 +9009,28 @@
         <v>0.0571</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1324021328215657</v>
+        <v>0.1166779786345853</v>
       </c>
       <c r="J4" t="n">
+        <v>255</v>
+      </c>
+      <c r="K4" t="n">
         <v>254</v>
       </c>
-      <c r="K4" t="n">
-        <v>253</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.008458576263899897</v>
+        <v>0.006540117114535504</v>
       </c>
       <c r="M4" t="n">
-        <v>8.226501539381399</v>
+        <v>8.250625224876298</v>
       </c>
       <c r="N4" t="n">
-        <v>110.088335101436</v>
+        <v>111.2620622235656</v>
       </c>
       <c r="O4" t="n">
-        <v>10.49229884731825</v>
+        <v>10.5480833436016</v>
       </c>
       <c r="P4" t="n">
-        <v>321.355935801359</v>
+        <v>321.5205584564778</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -9037,7 +9068,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E255"/>
+  <dimension ref="A1:E256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15921,6 +15952,33 @@
         </is>
       </c>
     </row>
+    <row r="256">
+      <c r="A256" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-22 22:05:56+00:00</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>-36.14804317497099,175.44040666358663</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>-36.14877302925327,175.44091072735006</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>-36.14916545752158,175.44166652321843</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0116/nzd0116.xlsx
+++ b/data/nzd0116/nzd0116.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E256"/>
+  <dimension ref="A1:E257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5806,6 +5806,27 @@
         <v>304.49</v>
       </c>
       <c r="E256" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:05:54+00:00</t>
+        </is>
+      </c>
+      <c r="B257" t="n">
+        <v>351.05</v>
+      </c>
+      <c r="C257" t="n">
+        <v>306.01</v>
+      </c>
+      <c r="D257" t="n">
+        <v>305.62</v>
+      </c>
+      <c r="E257" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -5822,7 +5843,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B286"/>
+  <dimension ref="A1:B287"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8685,6 +8706,16 @@
       </c>
       <c r="B286" t="n">
         <v>0.67</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B287" t="n">
+        <v>1.11</v>
       </c>
     </row>
   </sheetData>
@@ -8853,28 +8884,28 @@
         <v>0.0281</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1034354006600475</v>
+        <v>0.09591792228527253</v>
       </c>
       <c r="J2" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K2" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L2" t="n">
-        <v>0.005371512187296479</v>
+        <v>0.004643979935869402</v>
       </c>
       <c r="M2" t="n">
-        <v>8.42270791959545</v>
+        <v>8.421990353801425</v>
       </c>
       <c r="N2" t="n">
-        <v>107.6642973277303</v>
+        <v>107.6206912276901</v>
       </c>
       <c r="O2" t="n">
-        <v>10.37614077235512</v>
+        <v>10.37403929179421</v>
       </c>
       <c r="P2" t="n">
-        <v>358.2281237293733</v>
+        <v>358.3063872606905</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -8931,28 +8962,28 @@
         <v>0.0663</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3536849567698716</v>
+        <v>0.3388084658759654</v>
       </c>
       <c r="J3" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K3" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05351843832680192</v>
+        <v>0.04913638415698218</v>
       </c>
       <c r="M3" t="n">
-        <v>8.968555776738308</v>
+        <v>8.998122718830402</v>
       </c>
       <c r="N3" t="n">
-        <v>120.229456053133</v>
+        <v>121.2360229454279</v>
       </c>
       <c r="O3" t="n">
-        <v>10.96491933637147</v>
+        <v>11.0107230891267</v>
       </c>
       <c r="P3" t="n">
-        <v>316.3062265655955</v>
+        <v>316.4611038599385</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -9009,28 +9040,28 @@
         <v>0.0571</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1166779786345853</v>
+        <v>0.1021310554335975</v>
       </c>
       <c r="J4" t="n">
+        <v>256</v>
+      </c>
+      <c r="K4" t="n">
         <v>255</v>
       </c>
-      <c r="K4" t="n">
-        <v>254</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.006540117114535504</v>
+        <v>0.004997209841851702</v>
       </c>
       <c r="M4" t="n">
-        <v>8.250625224876298</v>
+        <v>8.271352988639391</v>
       </c>
       <c r="N4" t="n">
-        <v>111.2620622235656</v>
+        <v>112.2179872585621</v>
       </c>
       <c r="O4" t="n">
-        <v>10.5480833436016</v>
+        <v>10.59329916780236</v>
       </c>
       <c r="P4" t="n">
-        <v>321.5205584564778</v>
+        <v>321.6731617436561</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -9068,7 +9099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E256"/>
+  <dimension ref="A1:E257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15979,6 +16010,33 @@
         </is>
       </c>
     </row>
+    <row r="257">
+      <c r="A257" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:05:54+00:00</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>-36.14803615975044,175.44041189719863</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>-36.148768558007724,175.44091406307334</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>-36.14915674627785,175.441673022101</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0116/nzd0116.xlsx
+++ b/data/nzd0116/nzd0116.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E257"/>
+  <dimension ref="A1:E258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5827,6 +5827,27 @@
         <v>305.62</v>
       </c>
       <c r="E257" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:05:44+00:00</t>
+        </is>
+      </c>
+      <c r="B258" t="n">
+        <v>347.68</v>
+      </c>
+      <c r="C258" t="n">
+        <v>307.45</v>
+      </c>
+      <c r="D258" t="n">
+        <v>307.09</v>
+      </c>
+      <c r="E258" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -5843,7 +5864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B287"/>
+  <dimension ref="A1:B288"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8716,6 +8737,16 @@
       </c>
       <c r="B287" t="n">
         <v>1.11</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B288" t="n">
+        <v>0.49</v>
       </c>
     </row>
   </sheetData>
@@ -8884,28 +8915,28 @@
         <v>0.0281</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09591792228527253</v>
+        <v>0.08595816614624811</v>
       </c>
       <c r="J2" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="K2" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004643979935869402</v>
+        <v>0.003740393267966491</v>
       </c>
       <c r="M2" t="n">
-        <v>8.421990353801425</v>
+        <v>8.431309479552141</v>
       </c>
       <c r="N2" t="n">
-        <v>107.6206912276901</v>
+        <v>107.8661257707762</v>
       </c>
       <c r="O2" t="n">
-        <v>10.37403929179421</v>
+        <v>10.38586182128263</v>
       </c>
       <c r="P2" t="n">
-        <v>358.3063872606905</v>
+        <v>358.410495239398</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -8962,28 +8993,28 @@
         <v>0.0663</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3388084658759654</v>
+        <v>0.3252375333598402</v>
       </c>
       <c r="J3" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="K3" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04913638415698218</v>
+        <v>0.04536725275896913</v>
       </c>
       <c r="M3" t="n">
-        <v>8.998122718830402</v>
+        <v>9.021681640280045</v>
       </c>
       <c r="N3" t="n">
-        <v>121.2360229454279</v>
+        <v>121.9974367886788</v>
       </c>
       <c r="O3" t="n">
-        <v>11.0107230891267</v>
+        <v>11.04524498545319</v>
       </c>
       <c r="P3" t="n">
-        <v>316.4611038599385</v>
+        <v>316.6029589750343</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -9040,28 +9071,28 @@
         <v>0.0571</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1021310554335975</v>
+        <v>0.08893617231531585</v>
       </c>
       <c r="J4" t="n">
+        <v>257</v>
+      </c>
+      <c r="K4" t="n">
         <v>256</v>
       </c>
-      <c r="K4" t="n">
-        <v>255</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.004997209841851702</v>
+        <v>0.003786224008706984</v>
       </c>
       <c r="M4" t="n">
-        <v>8.271352988639391</v>
+        <v>8.288447126562104</v>
       </c>
       <c r="N4" t="n">
-        <v>112.2179872585621</v>
+        <v>112.9294554080198</v>
       </c>
       <c r="O4" t="n">
-        <v>10.59329916780236</v>
+        <v>10.62682715621271</v>
       </c>
       <c r="P4" t="n">
-        <v>321.6731617436561</v>
+        <v>321.8121357121906</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -9099,7 +9130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E257"/>
+  <dimension ref="A1:E258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16037,6 +16068,33 @@
         </is>
       </c>
     </row>
+    <row r="258">
+      <c r="A258" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:05:44+00:00</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>-36.148062139192575,175.44039251557604</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>-36.14875745698394,175.4409223448675</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>-36.14914541395147,175.4416814763975</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0116/nzd0116.xlsx
+++ b/data/nzd0116/nzd0116.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E258"/>
+  <dimension ref="A1:E259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5848,6 +5848,27 @@
         <v>307.09</v>
       </c>
       <c r="E258" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B259" t="n">
+        <v>348.09</v>
+      </c>
+      <c r="C259" t="n">
+        <v>310.32</v>
+      </c>
+      <c r="D259" t="n">
+        <v>311.82</v>
+      </c>
+      <c r="E259" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -5864,7 +5885,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B288"/>
+  <dimension ref="A1:B290"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8747,6 +8768,26 @@
       </c>
       <c r="B288" t="n">
         <v>0.49</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B289" t="n">
+        <v>-0.45</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B290" t="n">
+        <v>-0.58</v>
       </c>
     </row>
   </sheetData>
@@ -8915,28 +8956,28 @@
         <v>0.0281</v>
       </c>
       <c r="I2" t="n">
-        <v>0.08595816614624811</v>
+        <v>0.07637861954841729</v>
       </c>
       <c r="J2" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="K2" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003740393267966491</v>
+        <v>0.002963319244255747</v>
       </c>
       <c r="M2" t="n">
-        <v>8.431309479552141</v>
+        <v>8.438329056450453</v>
       </c>
       <c r="N2" t="n">
-        <v>107.8661257707762</v>
+        <v>108.0550224632668</v>
       </c>
       <c r="O2" t="n">
-        <v>10.38586182128263</v>
+        <v>10.39495177782306</v>
       </c>
       <c r="P2" t="n">
-        <v>358.410495239398</v>
+        <v>358.5114234584345</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -8993,28 +9034,28 @@
         <v>0.0663</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3252375333598402</v>
+        <v>0.3139188791645485</v>
       </c>
       <c r="J3" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="K3" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04536725275896913</v>
+        <v>0.04245050501239833</v>
       </c>
       <c r="M3" t="n">
-        <v>9.021681640280045</v>
+        <v>9.035402510872123</v>
       </c>
       <c r="N3" t="n">
-        <v>121.9974367886788</v>
+        <v>122.3719538245929</v>
       </c>
       <c r="O3" t="n">
-        <v>11.04524498545319</v>
+        <v>11.06218576162021</v>
       </c>
       <c r="P3" t="n">
-        <v>316.6029589750343</v>
+        <v>316.7222100897039</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -9071,28 +9112,28 @@
         <v>0.0571</v>
       </c>
       <c r="I4" t="n">
-        <v>0.08893617231531585</v>
+        <v>0.07946250738022057</v>
       </c>
       <c r="J4" t="n">
+        <v>258</v>
+      </c>
+      <c r="K4" t="n">
         <v>257</v>
       </c>
-      <c r="K4" t="n">
-        <v>256</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.003786224008706984</v>
+        <v>0.003034314972551133</v>
       </c>
       <c r="M4" t="n">
-        <v>8.288447126562104</v>
+        <v>8.291698948277265</v>
       </c>
       <c r="N4" t="n">
-        <v>112.9294554080198</v>
+        <v>113.0755135849849</v>
       </c>
       <c r="O4" t="n">
-        <v>10.62682715621271</v>
+        <v>10.63369707980178</v>
       </c>
       <c r="P4" t="n">
-        <v>321.8121357121906</v>
+        <v>321.9127021004192</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -9130,7 +9171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E258"/>
+  <dimension ref="A1:E259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16095,6 +16136,33 @@
         </is>
       </c>
     </row>
+    <row r="259">
+      <c r="A259" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>-36.148058978489075,175.44039487357827</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>-36.1487353320253,175.4409388509365</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>-36.1491089500678,175.4417086796619</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0116/nzd0116.xlsx
+++ b/data/nzd0116/nzd0116.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E259"/>
+  <dimension ref="A1:E260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5869,6 +5869,27 @@
         <v>311.82</v>
       </c>
       <c r="E259" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:04:44+00:00</t>
+        </is>
+      </c>
+      <c r="B260" t="n">
+        <v>341.83</v>
+      </c>
+      <c r="C260" t="n">
+        <v>308.25</v>
+      </c>
+      <c r="D260" t="n">
+        <v>309.34</v>
+      </c>
+      <c r="E260" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -5885,7 +5906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B290"/>
+  <dimension ref="A1:B291"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8788,6 +8809,16 @@
       </c>
       <c r="B290" t="n">
         <v>-0.58</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B291" t="n">
+        <v>0.26</v>
       </c>
     </row>
   </sheetData>
@@ -8956,28 +8987,28 @@
         <v>0.0281</v>
       </c>
       <c r="I2" t="n">
-        <v>0.07637861954841729</v>
+        <v>0.06208771039522175</v>
       </c>
       <c r="J2" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K2" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002963319244255747</v>
+        <v>0.001952493840330582</v>
       </c>
       <c r="M2" t="n">
-        <v>8.438329056450453</v>
+        <v>8.465416684252517</v>
       </c>
       <c r="N2" t="n">
-        <v>108.0550224632668</v>
+        <v>108.9731239571141</v>
       </c>
       <c r="O2" t="n">
-        <v>10.39495177782306</v>
+        <v>10.43901930054323</v>
       </c>
       <c r="P2" t="n">
-        <v>358.5114234584345</v>
+        <v>358.6631512450383</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -9034,28 +9065,28 @@
         <v>0.0663</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3139188791645485</v>
+        <v>0.3010648229191509</v>
       </c>
       <c r="J3" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K3" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04245050501239833</v>
+        <v>0.03916358107022311</v>
       </c>
       <c r="M3" t="n">
-        <v>9.035402510872123</v>
+        <v>9.054906433948689</v>
       </c>
       <c r="N3" t="n">
-        <v>122.3719538245929</v>
+        <v>122.9797650723282</v>
       </c>
       <c r="O3" t="n">
-        <v>11.06218576162021</v>
+        <v>11.08962420789488</v>
       </c>
       <c r="P3" t="n">
-        <v>316.7222100897039</v>
+        <v>316.8586826879192</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -9112,28 +9143,28 @@
         <v>0.0571</v>
       </c>
       <c r="I4" t="n">
-        <v>0.07946250738022057</v>
+        <v>0.06814194521460788</v>
       </c>
       <c r="J4" t="n">
+        <v>259</v>
+      </c>
+      <c r="K4" t="n">
         <v>258</v>
       </c>
-      <c r="K4" t="n">
-        <v>257</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.003034314972551133</v>
+        <v>0.002235686714829987</v>
       </c>
       <c r="M4" t="n">
-        <v>8.291698948277265</v>
+        <v>8.301823818004154</v>
       </c>
       <c r="N4" t="n">
-        <v>113.0755135849849</v>
+        <v>113.4635498188498</v>
       </c>
       <c r="O4" t="n">
-        <v>10.63369707980178</v>
+        <v>10.65192704719901</v>
       </c>
       <c r="P4" t="n">
-        <v>321.9127021004192</v>
+        <v>322.0337941186817</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -9171,7 +9202,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E259"/>
+  <dimension ref="A1:E260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16163,6 +16194,33 @@
         </is>
       </c>
     </row>
+    <row r="260">
+      <c r="A260" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:04:44+00:00</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>-36.14810723703064,175.44035887088992</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>-36.14875128974828,175.44092694586325</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>-36.14912806855293,175.44169441664263</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0116/nzd0116.xlsx
+++ b/data/nzd0116/nzd0116.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E260"/>
+  <dimension ref="A1:E262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5892,6 +5892,48 @@
       <c r="E260" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:04:54+00:00</t>
+        </is>
+      </c>
+      <c r="B261" t="n">
+        <v>334.51</v>
+      </c>
+      <c r="C261" t="n">
+        <v>306.96</v>
+      </c>
+      <c r="D261" t="n">
+        <v>307.56</v>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:06+00:00</t>
+        </is>
+      </c>
+      <c r="B262" t="n">
+        <v>324.56</v>
+      </c>
+      <c r="C262" t="n">
+        <v>304.47</v>
+      </c>
+      <c r="D262" t="n">
+        <v>304.56</v>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -5906,7 +5948,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B291"/>
+  <dimension ref="A1:B293"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8819,6 +8861,26 @@
       </c>
       <c r="B291" t="n">
         <v>0.26</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B292" t="n">
+        <v>-0.68</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>-0.7</v>
       </c>
     </row>
   </sheetData>
@@ -8987,28 +9049,28 @@
         <v>0.0281</v>
       </c>
       <c r="I2" t="n">
-        <v>0.06208771039522175</v>
+        <v>0.01581337922758985</v>
       </c>
       <c r="J2" t="n">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K2" t="n">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001952493840330582</v>
+        <v>0.0001208914748676015</v>
       </c>
       <c r="M2" t="n">
-        <v>8.465416684252517</v>
+        <v>8.599405595659716</v>
       </c>
       <c r="N2" t="n">
-        <v>108.9731239571141</v>
+        <v>115.415300039418</v>
       </c>
       <c r="O2" t="n">
-        <v>10.43901930054323</v>
+        <v>10.7431513085974</v>
       </c>
       <c r="P2" t="n">
-        <v>358.6631512450383</v>
+        <v>359.1563846353018</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -9065,28 +9127,28 @@
         <v>0.0663</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3010648229191509</v>
+        <v>0.2722379040518462</v>
       </c>
       <c r="J3" t="n">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K3" t="n">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03916358107022311</v>
+        <v>0.03207618376476473</v>
       </c>
       <c r="M3" t="n">
-        <v>9.054906433948689</v>
+        <v>9.106557020471183</v>
       </c>
       <c r="N3" t="n">
-        <v>122.9797650723282</v>
+        <v>124.8009417466982</v>
       </c>
       <c r="O3" t="n">
-        <v>11.08962420789488</v>
+        <v>11.17143418486177</v>
       </c>
       <c r="P3" t="n">
-        <v>316.8586826879192</v>
+        <v>317.1659175329975</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -9143,28 +9205,28 @@
         <v>0.0571</v>
       </c>
       <c r="I4" t="n">
-        <v>0.06814194521460788</v>
+        <v>0.0411635649789177</v>
       </c>
       <c r="J4" t="n">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K4" t="n">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002235686714829987</v>
+        <v>0.0008135317572407486</v>
       </c>
       <c r="M4" t="n">
-        <v>8.301823818004154</v>
+        <v>8.339861575791993</v>
       </c>
       <c r="N4" t="n">
-        <v>113.4635498188498</v>
+        <v>114.9845498446317</v>
       </c>
       <c r="O4" t="n">
-        <v>10.65192704719901</v>
+        <v>10.72308490335834</v>
       </c>
       <c r="P4" t="n">
-        <v>322.0337941186817</v>
+        <v>322.3234789223553</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -9202,7 +9264,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E260"/>
+  <dimension ref="A1:E262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16221,6 +16283,60 @@
         </is>
       </c>
     </row>
+    <row r="261">
+      <c r="A261" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:04:54+00:00</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>-36.14816366713432,175.44031677184515</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>-36.14876123441571,175.44091952675723</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>-36.14914179069056,175.44168417947137</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:06+00:00</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>-36.14824037196753,175.4402595469562</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>-36.14878042993539,175.44090520615208</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>-36.14916491788703,175.4416669258041</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
